--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -3072,7 +3072,7 @@
         <v>136150004</v>
       </c>
       <c r="B23" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>136149902</v>
       </c>
       <c r="B24" t="n">
-        <v>92675</v>
+        <v>92678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>136148101</v>
       </c>
       <c r="B27" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>136271230</v>
       </c>
       <c r="B109" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>136177837</v>
       </c>
       <c r="B207" t="n">
-        <v>106653</v>
+        <v>106656</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -3198,7 +3198,7 @@
         <v>136149902</v>
       </c>
       <c r="B24" t="n">
-        <v>92678</v>
+        <v>92679</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>136271230</v>
       </c>
       <c r="B109" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>136177837</v>
       </c>
       <c r="B207" t="n">
-        <v>106656</v>
+        <v>106657</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -3072,7 +3072,7 @@
         <v>136150004</v>
       </c>
       <c r="B23" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>136149902</v>
       </c>
       <c r="B24" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>136148101</v>
       </c>
       <c r="B27" t="n">
-        <v>89334</v>
+        <v>89336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136148724</v>
       </c>
       <c r="B31" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>136271230</v>
       </c>
       <c r="B109" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>136168429</v>
       </c>
       <c r="B110" t="n">
-        <v>79753</v>
+        <v>79755</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>136177837</v>
       </c>
       <c r="B207" t="n">
-        <v>106657</v>
+        <v>106662</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -13120,7 +13120,7 @@
         <v>136271230</v>
       </c>
       <c r="B109" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>136177837</v>
       </c>
       <c r="B207" t="n">
-        <v>106662</v>
+        <v>106664</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ288"/>
+  <dimension ref="A1:AZ289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31466,58 +31466,56 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>121560121</v>
+        <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>101326</v>
+        <v>110070</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>222498</v>
+        <v>220204</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Bäckmyren, Bäckmyren, Jmt</t>
+          <t>Åsmundgården, Jmt</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>492551</v>
+        <v>488238</v>
       </c>
       <c r="R278" t="n">
-        <v>7015980</v>
+        <v>7017033</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -31541,12 +31539,12 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -31555,78 +31553,83 @@
       <c r="AE278" t="b">
         <v>0</v>
       </c>
+      <c r="AF278" t="inlineStr"/>
       <c r="AG278" t="b">
         <v>0</v>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY278" t="inlineStr"/>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121560121</t>
+          <t>https://artportalen.se/Sighting/136949677</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>119817264</v>
+        <v>121560121</v>
       </c>
       <c r="B279" t="n">
-        <v>57953</v>
+        <v>101326</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Storfetten, Storfetten, Jmt</t>
+          <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>501579</v>
+        <v>492551</v>
       </c>
       <c r="R279" t="n">
-        <v>7014000</v>
+        <v>7015980</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -31653,17 +31656,12 @@
       </c>
       <c r="Y279" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC279" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -31674,31 +31672,36 @@
       </c>
       <c r="AG279" t="b">
         <v>0</v>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119817264</t>
+          <t>https://artportalen.se/Sighting/121560121</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>133884020</v>
+        <v>119817264</v>
       </c>
       <c r="B280" t="n">
-        <v>58231</v>
+        <v>57953</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31706,37 +31709,42 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>102980</v>
+        <v>100109</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Fjälån, Jmt</t>
+          <t>Storfetten, Storfetten, Jmt</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>500548</v>
+        <v>501579</v>
       </c>
       <c r="R280" t="n">
-        <v>7014163</v>
+        <v>7014000</v>
       </c>
       <c r="S280" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -31760,12 +31768,17 @@
       </c>
       <c r="Y280" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -31780,57 +31793,52 @@
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133884020</t>
+          <t>https://artportalen.se/Sighting/119817264</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>133884000</v>
+        <v>133884020</v>
       </c>
       <c r="B281" t="n">
-        <v>58234</v>
+        <v>58231</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>102981</v>
+        <v>102980</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P281" t="inlineStr">
         <is>
           <t>Fjälån, Jmt</t>
@@ -31898,16 +31906,16 @@
       <c r="AY281" t="inlineStr"/>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133884000</t>
+          <t>https://artportalen.se/Sighting/133884020</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>15772027</v>
+        <v>133884000</v>
       </c>
       <c r="B282" t="n">
-        <v>10000</v>
+        <v>58234</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31915,41 +31923,42 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100196</v>
+        <v>102981</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Hussvala</t>
+        </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Agathidium pallidum</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1827)</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>MidskogF14, Jmt</t>
+          <t>Fjälån, Jmt</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>509456</v>
+        <v>500548</v>
       </c>
       <c r="R282" t="n">
-        <v>7012087</v>
+        <v>7014163</v>
       </c>
       <c r="S282" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -31973,17 +31982,12 @@
       </c>
       <c r="Y282" t="inlineStr">
         <is>
-          <t>2013-05-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>2013-06-21</t>
-        </is>
-      </c>
-      <c r="AC282" t="inlineStr">
-        <is>
-          <t>Lövbrännan med hög lövandel, mkt björk och en del asp, hyggligt med björkved</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -31994,62 +31998,48 @@
       </c>
       <c r="AG282" t="b">
         <v>0</v>
-      </c>
-      <c r="AI282" t="inlineStr">
-        <is>
-          <t>Lövbränna, björkhögstubbe och låga, båda med fnösketickor.</t>
-        </is>
       </c>
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Lars-Olof Grund</t>
+          <t>Pattranit Kwanruen</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Lars-Olof Grund</t>
-        </is>
-      </c>
-      <c r="AY282" t="inlineStr">
-        <is>
-          <t>ÅGP-inventering björk och asp Norrland</t>
-        </is>
-      </c>
+          <t>Pattranit Kwanruen</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr"/>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15772027</t>
+          <t>https://artportalen.se/Sighting/133884000</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>15772038</v>
+        <v>15772027</v>
       </c>
       <c r="B283" t="n">
-        <v>8728</v>
+        <v>10000</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100798</v>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>Smal trollknäppare</t>
-        </is>
+        <v>100196</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Agathidium pallidum</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(Gyllenhal, 1827)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -32098,12 +32088,12 @@
       </c>
       <c r="Y283" t="inlineStr">
         <is>
+          <t>2013-05-18</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
           <t>2013-06-21</t>
-        </is>
-      </c>
-      <c r="AA283" t="inlineStr">
-        <is>
-          <t>2013-07-18</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -32143,38 +32133,38 @@
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15772038</t>
+          <t>https://artportalen.se/Sighting/15772027</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>15771999</v>
+        <v>15772038</v>
       </c>
       <c r="B284" t="n">
-        <v>4819</v>
+        <v>8728</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100857</v>
+        <v>100798</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Robust tickgnagare</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Dorcatoma robusta</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Strand, 1938</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -32182,9 +32172,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>MidskogF13, Jmt</t>
+          <t>MidskogF14, Jmt</t>
         </is>
       </c>
       <c r="Q284" t="n">
@@ -32242,7 +32237,7 @@
       </c>
       <c r="AI284" t="inlineStr">
         <is>
-          <t>Lövbränna, asphögstubbe +låga</t>
+          <t>Lövbränna, björkhögstubbe och låga, båda med fnösketickor.</t>
         </is>
       </c>
       <c r="AT284" t="inlineStr"/>
@@ -32263,38 +32258,38 @@
       </c>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15771999</t>
+          <t>https://artportalen.se/Sighting/15772038</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>15772034</v>
+        <v>15771999</v>
       </c>
       <c r="B285" t="n">
-        <v>12370</v>
+        <v>4819</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>101465</v>
+        <v>100857</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Gulbandad brunbagge</t>
+          <t>Robust tickgnagare</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Orchesia fasciata</t>
+          <t>Dorcatoma robusta</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Illiger, 1798)</t>
+          <t>Strand, 1938</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -32302,14 +32297,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N285" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>MidskogF14, Jmt</t>
+          <t>MidskogF13, Jmt</t>
         </is>
       </c>
       <c r="Q285" t="n">
@@ -32343,12 +32333,12 @@
       </c>
       <c r="Y285" t="inlineStr">
         <is>
-          <t>2013-05-18</t>
+          <t>2013-06-21</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>2013-06-21</t>
+          <t>2013-07-18</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -32367,7 +32357,7 @@
       </c>
       <c r="AI285" t="inlineStr">
         <is>
-          <t>Lövbränna, björkhögstubbe och låga, båda med fnösketickor.</t>
+          <t>Lövbränna, asphögstubbe +låga</t>
         </is>
       </c>
       <c r="AT285" t="inlineStr"/>
@@ -32388,38 +32378,38 @@
       </c>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15772034</t>
+          <t>https://artportalen.se/Sighting/15771999</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>15771980</v>
+        <v>15772034</v>
       </c>
       <c r="B286" t="n">
-        <v>4872</v>
+        <v>12370</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>101675</v>
+        <v>101465</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Gulbandad brunbagge</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Orchesia fasciata</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Illiger, 1798)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -32427,9 +32417,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>MidskogF13, Jmt</t>
+          <t>MidskogF14, Jmt</t>
         </is>
       </c>
       <c r="Q286" t="n">
@@ -32463,14 +32458,14 @@
       </c>
       <c r="Y286" t="inlineStr">
         <is>
+          <t>2013-05-18</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
           <t>2013-06-21</t>
         </is>
       </c>
-      <c r="AA286" t="inlineStr">
-        <is>
-          <t>2013-07-18</t>
-        </is>
-      </c>
       <c r="AC286" t="inlineStr">
         <is>
           <t>Lövbrännan med hög lövandel, mkt björk och en del asp, hyggligt med björkved</t>
@@ -32487,7 +32482,7 @@
       </c>
       <c r="AI286" t="inlineStr">
         <is>
-          <t>Lövbränna, asphögstubbe +låga</t>
+          <t>Lövbränna, björkhögstubbe och låga, båda med fnösketickor.</t>
         </is>
       </c>
       <c r="AT286" t="inlineStr"/>
@@ -32508,16 +32503,16 @@
       </c>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15771980</t>
+          <t>https://artportalen.se/Sighting/15772034</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>15772025</v>
+        <v>15771980</v>
       </c>
       <c r="B287" t="n">
-        <v>4813</v>
+        <v>4872</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32525,16 +32520,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>105333</v>
+        <v>101675</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Aspvedgnagare</t>
+        </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Dorcatoma dresdensis</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Herbst, 1792</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -32542,14 +32542,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N287" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>MidskogF14, Jmt</t>
+          <t>MidskogF13, Jmt</t>
         </is>
       </c>
       <c r="Q287" t="n">
@@ -32583,12 +32578,12 @@
       </c>
       <c r="Y287" t="inlineStr">
         <is>
-          <t>2013-05-18</t>
+          <t>2013-06-21</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>2013-06-21</t>
+          <t>2013-07-18</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -32607,7 +32602,7 @@
       </c>
       <c r="AI287" t="inlineStr">
         <is>
-          <t>Lövbränna, björkhögstubbe och låga, båda med fnösketickor.</t>
+          <t>Lövbränna, asphögstubbe +låga</t>
         </is>
       </c>
       <c r="AT287" t="inlineStr"/>
@@ -32628,16 +32623,16 @@
       </c>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15772025</t>
+          <t>https://artportalen.se/Sighting/15771980</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>15772051</v>
+        <v>15772025</v>
       </c>
       <c r="B288" t="n">
-        <v>6274</v>
+        <v>4813</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32645,21 +32640,16 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>105336</v>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>Vanlig flatbagge</t>
-        </is>
+        <v>105333</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Dorcatoma dresdensis</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Herbst, 1792</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -32708,12 +32698,12 @@
       </c>
       <c r="Y288" t="inlineStr">
         <is>
+          <t>2013-05-18</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
           <t>2013-06-21</t>
-        </is>
-      </c>
-      <c r="AA288" t="inlineStr">
-        <is>
-          <t>2013-07-18</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -32752,6 +32742,131 @@
         </is>
       </c>
       <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15772025</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>15772051</v>
+      </c>
+      <c r="B289" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>MidskogF14, Jmt</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>509456</v>
+      </c>
+      <c r="R289" t="n">
+        <v>7012087</v>
+      </c>
+      <c r="S289" t="n">
+        <v>25</v>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>2013-06-21</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>2013-07-18</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>Lövbrännan med hög lövandel, mkt björk och en del asp, hyggligt med björkved</t>
+        </is>
+      </c>
+      <c r="AD289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>Lövbränna, björkhögstubbe och låga, båda med fnösketickor.</t>
+        </is>
+      </c>
+      <c r="AT289" t="inlineStr"/>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr">
+        <is>
+          <t>ÅGP-inventering björk och asp Norrland</t>
+        </is>
+      </c>
+      <c r="AZ289" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/15772051</t>
         </is>
@@ -33046,6 +33161,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -31469,7 +31469,7 @@
         <v>136949677</v>
       </c>
       <c r="B278" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
